--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG - Recusa MDS 18-07-2025.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG - Recusa MDS 18-07-2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19A70FD0-200F-4134-BC95-2D11A86071DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FC17F01-04BE-4E20-B85B-CE8422978B09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="12">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,37 +54,16 @@
     <t>Recusa MDS 18-07-2025</t>
   </si>
   <si>
-    <t>133316369</t>
+    <t>133464716</t>
   </si>
   <si>
     <t>971</t>
   </si>
   <si>
-    <t>Relatório de Recusa SICOOB 17.07.2025</t>
-  </si>
-  <si>
-    <t>133352234</t>
-  </si>
-  <si>
-    <t>133380494</t>
-  </si>
-  <si>
-    <t>133474361</t>
-  </si>
-  <si>
-    <t>133327436</t>
-  </si>
-  <si>
-    <t>133396433</t>
-  </si>
-  <si>
-    <t>130823617</t>
-  </si>
-  <si>
-    <t>133347191</t>
-  </si>
-  <si>
-    <t>133398139</t>
+    <t>Relatório de Recusa MDS 18.07.2025</t>
+  </si>
+  <si>
+    <t>133489026</t>
   </si>
 </sst>
 </file>
@@ -558,129 +537,31 @@
       <c r="F3"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>6</v>
-      </c>
+      <c r="D4" s="6"/>
       <c r="F4"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>6</v>
-      </c>
+      <c r="D5" s="6"/>
       <c r="F5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>6</v>
-      </c>
+      <c r="D6" s="6"/>
       <c r="F6"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>6</v>
-      </c>
+      <c r="D7" s="6"/>
       <c r="F7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>6</v>
-      </c>
+      <c r="D8" s="6"/>
       <c r="F8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>6</v>
-      </c>
+      <c r="D9" s="6"/>
       <c r="F9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>6</v>
-      </c>
+      <c r="D10" s="6"/>
       <c r="F10"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
